--- a/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Barrett's esophagus is a condition in which the following is always present:</t>
+          <t>Barrett's esophagus is a condition in which the following is always present</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ulcerative colitis is:</t>
+          <t>Ulcerative colitis is</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In patients with Burkitt lymphoma, especially in the endemic variant, previous infection with has been demonstrated:</t>
+          <t>In patients with Burkitt lymphoma, especially in the endemic variant, previous infection with has been demonstrated</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tophi are defined as:</t>
+          <t>Tophi are defined as</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dopamine:</t>
+          <t>Dopamine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The first-line treatment (the most important to administer) for anaphylactic shock involves the administration of:</t>
+          <t>The first-line treatment (the most important to administer) for anaphylactic shock involves the administration of</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A physician must perform radial artery cannulation for invasive arterial blood pressure monitoring. Before the procedure, it is advisable to perform:</t>
+          <t>A physician must perform radial artery cannulation for invasive arterial blood pressure monitoring. Before the procedure, it is advisable to perform</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A 45-year-old woman arrives at the Emergency Department in a coma and with respiratory depression; the physician administers naloxone hydrochloride 0.4 mg intravenously. Naloxone hydrochloride is:</t>
+          <t>A 45-year-old woman arrives at the Emergency Department in a coma and with respiratory depression; the physician administers naloxone hydrochloride 0.4 mg intravenously. Naloxone hydrochloride is</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Meckel's diverticulum is:</t>
+          <t>Meckel's diverticulum is</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A patient, not affected by Crohn's disease, complains of the discharge of pus from an orifice about 3 cm from the anal margin. A diagnosis of perianal fistula is made. The recommended treatment is:</t>
+          <t>A patient, not affected by Crohn's disease, complains of the discharge of pus from an orifice about 3 cm from the anal margin. A diagnosis of perianal fistula is made. The recommended treatment is</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A 62-year-old patient underwent a right hemicolectomy 3 years earlier for adenocarcinoma (pT2, N0, M0). During follow-up, a peripheral pulmonary nodule of the right upper lobe, 2 cm in diameter, is identified as the only site of uptake on a whole-body PET scan. CT-guided needle biopsy of the nodule demonstrated that it is metastatic adenocarcinoma. The patient has no other comorbidities. The recommended treatment is:</t>
+          <t>A 62-year-old patient underwent a right hemicolectomy 3 years earlier for adenocarcinoma (pT2, N0, M0). During follow-up, a peripheral pulmonary nodule of the right upper lobe, 2 cm in diameter, is identified as the only site of uptake on a whole-body PET scan. CT-guided needle biopsy of the nodule demonstrated that it is metastatic adenocarcinoma. The patient has no other comorbidities. The recommended treatment is</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>In the calculation of the specificity of a diagnostic test:</t>
+          <t>In the calculation of the specificity of a diagnostic test</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The law that established the National Health Service is:</t>
+          <t>The law that established the National Health Service is</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>The accuracy of a diagnostic test represents:</t>
+          <t>The accuracy of a diagnostic test represents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>A 65-year-old patient is scheduled to undergo cholecystectomy. During pre-admission, he underwent a chest radiograph. The radiographic image shown in the figure is, in the first instance, consistent with:</t>
+          <t>A 65-year-old patient is scheduled to undergo cholecystectomy. During pre-admission, he underwent a chest radiograph. The radiographic image shown in the figure is, in the first instance, consistent with</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>An Emergency Department physician is evaluating a 54-year-old man complaining of retrosternal pain. The pain does not improve and the patient suddenly loses consciousness. In the figure, the rhythm shown on the monitor is:</t>
+          <t>An Emergency Department physician is evaluating a 54-year-old man complaining of retrosternal pain. The pain does not improve and the patient suddenly loses consciousness. In the figure, the rhythm shown on the monitor is</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>An Emergency Department physician is evaluating a 54-year-old man complaining of retrosternal pain. The pain does not improve and the patient suddenly loses consciousness. The first-line treatment is:</t>
+          <t>An Emergency Department physician is evaluating a 54-year-old man complaining of retrosternal pain. The pain does not improve and the patient suddenly loses consciousness. The first-line treatment is</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Phalen's maneuver may elicit painful symptoms in patients affected by:</t>
+          <t>Phalen's maneuver may elicit painful symptoms in patients affected by</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>On August 13, 2011, at 8 p.m., in Sicily, a forensic pathologist is contacted by the Public Prosecutor, having been notified by law enforcement of the discovery of a body at the deceased's residence. Upon arriving at the scene, the forensic pathologist is informed by the police that, due to the acrid odor present in the apartment, the windows of all the rooms in the house had been opened. The on-site examination begins; the body appears as shown in the figure. In light of the attached image and the data reported, considering a complete resolution of rigor mortis, it can be preliminarily estimated that the time elapsed is:</t>
+          <t>On August 13, 2011, at 8 p.m., in Sicily, a forensic pathologist is contacted by the Public Prosecutor, having been notified by law enforcement of the discovery of a body at the deceased's residence. Upon arriving at the scene, the forensic pathologist is informed by the police that, due to the acrid odor present in the apartment, the windows of all the rooms in the house had been opened. The on-site examination begins; the body appears as shown in the figure. In light of the attached image and the data reported, considering a complete resolution of rigor mortis, it can be preliminarily estimated that the time elapsed is</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>A 30-year-old patient presents for neurological evaluation regarding headache. The symptoms first appeared one year earlier. The pain was localized in the right orbital and supraorbital region and lasted up to a maximum of 3 hours. It was associated with conjunctival hyperemia, lacrimation, and palpebral edema, all ipsilateral. The episodes continued to occur on a daily basis for about a month and then ceased completely. After several months free of these symptoms, the headache has recurred for about a week with unchanged features. The most likely diagnosis is:</t>
+          <t>A 30-year-old patient presents for neurological evaluation regarding headache. The symptoms first appeared one year earlier. The pain was localized in the right orbital and supraorbital region and lasted up to a maximum of 3 hours. It was associated with conjunctival hyperemia, lacrimation, and palpebral edema, all ipsilateral. The episodes continued to occur on a daily basis for about a month and then ceased completely. After several months free of these symptoms, the headache has recurred for about a week with unchanged features. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A 32-year-old pregnant woman, with symptoms attributable to pre-eclampsia, subacutely develops headache, visual disturbance, confusional state, and seizures in rapid succession. Brain MRI with and without contrast reveals areas of T2 hyperintensity in the bilateral parieto-occipital regions. The most likely diagnosis is:</t>
+          <t>A 32-year-old pregnant woman, with symptoms attributable to pre-eclampsia, subacutely develops headache, visual disturbance, confusional state, and seizures in rapid succession. Brain MRI with and without contrast reveals areas of T2 hyperintensity in the bilateral parieto-occipital regions. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>In the case of cataract surgery using the femtosecond laser technique, it is correct to state that:</t>
+          <t>In the case of cataract surgery using the femtosecond laser technique, it is correct to state that</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A man presents to the physician complaining of persistent floaters and photopsias for 2 days; fundus examination reveals a peripheral horseshoe-shaped retinal tear without surrounding retinal detachment; visual acuity is perfectly preserved. The most appropriate therapy involves:</t>
+          <t>A man presents to the physician complaining of persistent floaters and photopsias for 2 days; fundus examination reveals a peripheral horseshoe-shaped retinal tear without surrounding retinal detachment; visual acuity is perfectly preserved. The most appropriate therapy involves</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Following placental abruption, a newborn experiences prolonged hypoxia. Hypoxic-ischemic encephalopathy (HIE) is one of the most commonly recognized causes of cerebral palsy (6-23%); cerebral hypothermia is currently the treatment of choice for HIE. The following are considered eligible for this treatment:</t>
+          <t>Following placental abruption, a newborn experiences prolonged hypoxia. Hypoxic-ischemic encephalopathy (HIE) is one of the most commonly recognized causes of cerebral palsy (6-23%); cerebral hypothermia is currently the treatment of choice for HIE. The following are considered eligible for this treatment</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Infectious Diseases</t>
+          <t>Infectious Diseases; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Nephrology</t>
+          <t>Nephrology; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Pharmacology and Toxicology</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Endocrinology; Nephrology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Pulmonology and Thoracic Surgery</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Nephrology; Endocrinology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Gynecology and Obstetrics</t>
+          <t>Dermatology and Venereology; Infectious Diseases</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Nephrology; Immunology and Rheumatology</t>
+          <t>Immunology and Rheumatology; Nephrology</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Oncology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Ophthalmology; Pediatrics</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Oncology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>General Surgery; Pediatrics</t>
+          <t>Otorhinolaryngology; Pediatrics</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Oncology</t>
+          <t>Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2018_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,6 +1557,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,6 +1746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1704,6 +1809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1762,6 +1872,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,6 +1935,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1878,6 +1998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1936,6 +2061,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1994,6 +2124,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2052,6 +2187,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2110,6 +2250,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2170,10 +2315,15 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>images/2018/ssm20182143254.png</t>
         </is>
@@ -2236,6 +2386,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2294,6 +2449,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2352,6 +2512,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2410,6 +2575,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2468,6 +2638,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2526,6 +2701,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2584,6 +2764,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2642,6 +2827,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2700,6 +2890,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2758,6 +2953,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2816,6 +3016,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2874,6 +3079,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2932,6 +3142,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2990,6 +3205,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3048,6 +3268,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3106,6 +3331,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3164,6 +3394,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3222,6 +3457,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3280,6 +3520,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3338,6 +3583,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3396,6 +3646,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3454,6 +3709,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3512,6 +3772,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3570,6 +3835,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3628,6 +3898,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3686,6 +3961,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3744,6 +4024,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3802,6 +4087,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3862,10 +4152,15 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
           <t>Histological image</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>images/2018/ssm20182144704.png</t>
         </is>
@@ -3928,6 +4223,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3988,10 +4288,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>images/2018/ssm20182144804.png</t>
         </is>
@@ -4054,6 +4359,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4112,6 +4422,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4170,6 +4485,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4228,6 +4548,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4286,6 +4611,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4344,6 +4674,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4402,6 +4737,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4460,6 +4800,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4518,6 +4863,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4576,6 +4926,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4634,6 +4989,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4692,6 +5052,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4752,10 +5117,15 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>images/2018/ssm20182145454.png</t>
         </is>
@@ -4820,10 +5190,15 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>images/2018/ssm20182145504.png</t>
         </is>
@@ -4886,6 +5261,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4944,6 +5324,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5002,6 +5387,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5060,6 +5450,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5118,6 +5513,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5176,6 +5576,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5234,6 +5639,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5292,6 +5702,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5350,6 +5765,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5408,6 +5828,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5466,6 +5891,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5524,6 +5954,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5582,6 +6017,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5640,6 +6080,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5700,10 +6145,15 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
           <t>Forensic photograph</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146254.png</t>
         </is>
@@ -5766,6 +6216,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5824,6 +6279,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5882,6 +6342,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5940,6 +6405,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5998,6 +6468,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6058,10 +6533,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146554.png</t>
         </is>
@@ -6126,10 +6606,15 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
           <t>Brain MRI</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>images/2018/ssm20182146604.png</t>
         </is>
@@ -6192,6 +6677,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6250,6 +6740,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6308,6 +6803,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6366,6 +6866,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6424,6 +6929,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6482,6 +6992,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6540,6 +7055,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6598,6 +7118,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6656,6 +7181,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6714,6 +7244,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6772,6 +7307,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6830,6 +7370,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6888,6 +7433,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6948,10 +7498,15 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>Lower limb X-ray</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>images/2018/ssm20182147304.png</t>
         </is>
@@ -7014,6 +7569,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7072,6 +7632,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7130,6 +7695,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7188,6 +7758,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7246,6 +7821,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7304,6 +7884,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7362,6 +7947,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7420,6 +8010,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7478,6 +8073,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7536,6 +8136,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7594,6 +8199,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7652,6 +8262,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7710,6 +8325,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7768,6 +8388,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7826,6 +8451,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7884,6 +8514,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7942,6 +8577,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8000,6 +8640,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8058,6 +8703,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8116,6 +8766,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8174,6 +8829,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8232,6 +8892,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8290,6 +8955,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8348,6 +9018,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8406,6 +9081,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8464,6 +9144,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8522,6 +9207,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8580,6 +9270,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8638,6 +9333,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8694,6 +9394,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
